--- a/diseases/d124/1995-1999.xlsx
+++ b/diseases/d124/1995-1999.xlsx
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -22358,7 +22358,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26983,7 +26983,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28833,7 +28833,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29758,7 +29758,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -31608,7 +31608,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32923,7 +32923,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -33848,7 +33848,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34773,7 +34773,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36623,7 +36623,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37548,7 +37548,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38473,7 +38473,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -39398,7 +39398,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -41248,7 +41248,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -42173,7 +42173,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44413,7 +44413,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -45338,7 +45338,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -46263,7 +46263,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -47188,7 +47188,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48113,7 +48113,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -49038,7 +49038,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -50888,7 +50888,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -51813,7 +51813,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -52738,7 +52738,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53663,7 +53663,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -54588,7 +54588,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">

--- a/diseases/d124/1995-1999.xlsx
+++ b/diseases/d124/1995-1999.xlsx
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16218,7 +16218,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18558,7 +18558,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21053,6 +21053,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21433,7 +21438,7 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -21978,6 +21983,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22358,7 +22368,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22903,6 +22913,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23283,7 +23298,7 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN118" t="b">
@@ -23828,6 +23843,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24208,7 +24228,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24753,6 +24773,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25133,7 +25158,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -25678,6 +25703,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26058,7 +26088,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26603,6 +26633,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26983,7 +27018,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -27528,6 +27563,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27908,7 +27948,7 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28453,6 +28493,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28833,7 +28878,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -29378,6 +29423,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29758,7 +29808,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30303,6 +30353,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30683,7 +30738,7 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN158" t="b">
@@ -31228,6 +31283,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31608,7 +31668,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32543,6 +32603,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32923,7 +32988,7 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -33468,6 +33533,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33848,7 +33918,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34393,6 +34463,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34773,7 +34848,7 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN180" t="b">
@@ -35318,6 +35393,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35698,7 +35778,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36243,6 +36323,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36623,7 +36708,7 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN190" t="b">
@@ -37168,6 +37253,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37548,7 +37638,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38093,6 +38183,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38473,7 +38568,7 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN200" t="b">
@@ -39018,6 +39113,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39398,7 +39498,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -39943,6 +40043,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40323,7 +40428,7 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN210" t="b">
@@ -40868,6 +40973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41248,7 +41358,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -41793,6 +41903,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42173,7 +42288,7 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN220" t="b">
@@ -42718,6 +42833,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43098,7 +43218,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44033,6 +44153,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44413,7 +44538,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -44958,6 +45083,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45338,7 +45468,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -45883,6 +46013,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46263,7 +46398,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -46808,6 +46943,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47188,7 +47328,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -47733,6 +47873,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48113,7 +48258,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -48658,6 +48803,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49038,7 +49188,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -49583,6 +49733,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49963,7 +50118,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -50508,6 +50663,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50888,7 +51048,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -51433,6 +51593,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51813,7 +51978,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -52358,6 +52523,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52738,7 +52908,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53283,6 +53453,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53663,7 +53838,7 @@
       </c>
       <c r="AM282" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN282" t="b">
@@ -54208,6 +54383,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54588,7 +54768,7 @@
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN287" t="b">

--- a/diseases/d124/1995-1999.xlsx
+++ b/diseases/d124/1995-1999.xlsx
@@ -21048,6 +21048,11 @@
       <c r="Q106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21060,13 +21065,23 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -21963,6 +21978,11 @@
       <c r="Q111" t="n">
         <v>0</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21975,13 +21995,23 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -22878,6 +22908,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22890,13 +22925,23 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
       </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV116" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -23793,6 +23838,11 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23805,13 +23855,23 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -24708,6 +24768,11 @@
       <c r="Q126" t="n">
         <v>0</v>
       </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24720,13 +24785,23 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -25623,6 +25698,11 @@
       <c r="Q131" t="n">
         <v>0</v>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25635,13 +25715,23 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -26538,6 +26628,11 @@
       <c r="Q136" t="n">
         <v>0</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26550,13 +26645,23 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -27453,6 +27558,11 @@
       <c r="Q141" t="n">
         <v>0</v>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27465,13 +27575,23 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -28368,6 +28488,11 @@
       <c r="Q146" t="n">
         <v>0</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28380,13 +28505,23 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -29283,6 +29418,11 @@
       <c r="Q151" t="n">
         <v>0</v>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29295,13 +29435,23 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
       </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -30198,6 +30348,11 @@
       <c r="Q156" t="n">
         <v>0</v>
       </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30210,13 +30365,23 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
       </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV156" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -31113,6 +31278,11 @@
       <c r="Q161" t="n">
         <v>0</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31125,13 +31295,23 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -32418,6 +32598,11 @@
       <c r="Q168" t="n">
         <v>0</v>
       </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32430,13 +32615,23 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
       </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV168" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -33333,6 +33528,11 @@
       <c r="Q173" t="n">
         <v>0</v>
       </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33345,13 +33545,23 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
       </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -34248,6 +34458,11 @@
       <c r="Q178" t="n">
         <v>0</v>
       </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34260,13 +34475,23 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
       </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV178" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -35163,6 +35388,11 @@
       <c r="Q183" t="n">
         <v>0</v>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35175,13 +35405,23 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
       </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV183" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36078,6 +36318,11 @@
       <c r="Q188" t="n">
         <v>0</v>
       </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36090,13 +36335,23 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
       </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV188" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -36993,6 +37248,11 @@
       <c r="Q193" t="n">
         <v>0</v>
       </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37005,13 +37265,23 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
       </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV193" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -37908,6 +38178,11 @@
       <c r="Q198" t="n">
         <v>0</v>
       </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -37920,13 +38195,23 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR198" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -38823,6 +39108,11 @@
       <c r="Q203" t="n">
         <v>0</v>
       </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -38835,13 +39125,23 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR203" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
       </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV203" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -39738,6 +40038,11 @@
       <c r="Q208" t="n">
         <v>0</v>
       </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -39750,13 +40055,23 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
       </c>
+      <c r="AU208" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV208" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -40653,6 +40968,11 @@
       <c r="Q213" t="n">
         <v>0</v>
       </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -40665,13 +40985,23 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
         <v>0</v>
       </c>
+      <c r="AU213" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV213" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -41568,6 +41898,11 @@
       <c r="Q218" t="n">
         <v>0</v>
       </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -41580,13 +41915,23 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR218" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
       </c>
+      <c r="AU218" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV218" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -42483,6 +42828,11 @@
       <c r="Q223" t="n">
         <v>0</v>
       </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -42495,13 +42845,23 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
       </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV223" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -43788,6 +44148,11 @@
       <c r="Q230" t="n">
         <v>0</v>
       </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -43800,13 +44165,23 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -44703,6 +45078,11 @@
       <c r="Q235" t="n">
         <v>0</v>
       </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -44715,13 +45095,23 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
         <v>0</v>
       </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV235" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -45618,6 +46008,11 @@
       <c r="Q240" t="n">
         <v>0</v>
       </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -45630,13 +46025,23 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -46533,6 +46938,11 @@
       <c r="Q245" t="n">
         <v>0</v>
       </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -46545,13 +46955,23 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
         <v>0</v>
       </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV245" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -47448,6 +47868,11 @@
       <c r="Q250" t="n">
         <v>0</v>
       </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -47460,13 +47885,23 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
         <v>0</v>
       </c>
+      <c r="AU250" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV250" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -48363,6 +48798,11 @@
       <c r="Q255" t="n">
         <v>0</v>
       </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA255" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -48375,13 +48815,23 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS255" t="inlineStr"/>
       <c r="AT255" t="n">
         <v>0</v>
       </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV255" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -49278,6 +49728,11 @@
       <c r="Q260" t="n">
         <v>0</v>
       </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -49290,13 +49745,23 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
         <v>0</v>
       </c>
+      <c r="AU260" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV260" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -50193,6 +50658,11 @@
       <c r="Q265" t="n">
         <v>0</v>
       </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA265" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -50205,13 +50675,23 @@
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
         <v>0</v>
       </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV265" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -51108,6 +51588,11 @@
       <c r="Q270" t="n">
         <v>0</v>
       </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -51120,13 +51605,23 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
         <v>0</v>
       </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV270" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52023,6 +52518,11 @@
       <c r="Q275" t="n">
         <v>0</v>
       </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52035,13 +52535,23 @@
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS275" t="inlineStr"/>
       <c r="AT275" t="n">
         <v>0</v>
       </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV275" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -52938,6 +53448,11 @@
       <c r="Q280" t="n">
         <v>0</v>
       </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -52950,13 +53465,23 @@
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
         <v>0</v>
       </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV280" t="inlineStr">
         <is>
           <t>chp_notifiable</t>
@@ -53853,6 +54378,11 @@
       <c r="Q285" t="n">
         <v>0</v>
       </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA285" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -53865,12 +54395,22 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
         <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
